--- a/templates/hemodialysis_list_global_template.xlsx
+++ b/templates/hemodialysis_list_global_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{15A43D25-3A16-4749-84BE-47131F3E3692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C797A365-88E0-4D9D-8099-4E3F2037FAD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{3656BFD3-8587-4047-B8B7-EB5FDEC80029}"/>
   </bookViews>
@@ -113,7 +113,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -181,20 +181,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -217,6 +220,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -232,6 +244,61 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>10583</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>10583</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1588640</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>100116</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagem 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A284833B-EDC4-4940-8355-EC98686C15D6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="158750" y="201083"/>
+          <a:ext cx="4234473" cy="851533"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -554,7 +621,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A7:L57"/>
+  <dimension ref="A7:L58"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.140625" style="1" customWidth="1"/>
@@ -564,489 +631,499 @@
     <col min="5" max="5" width="36.5703125" style="1" customWidth="1"/>
     <col min="6" max="8" width="26.5703125" style="1" customWidth="1"/>
     <col min="9" max="9" width="2.140625" style="1" customWidth="1"/>
-    <col min="10" max="11" width="9.140625" hidden="1"/>
+    <col min="10" max="11" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="0" hidden="1" customWidth="1"/>
     <col min="13" max="16384" width="9.140625" hidden="1"/>
   </cols>
   <sheetData>
     <row r="7" spans="2:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
     </row>
     <row r="8" spans="2:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
     </row>
     <row r="9" spans="2:9" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
     </row>
     <row r="10" spans="2:9" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="11" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
     </row>
     <row r="12" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="13" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="5"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
     </row>
     <row r="14" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="7"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
     </row>
     <row r="15" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="7"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="7"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="5"/>
     </row>
     <row r="16" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="7"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
     </row>
     <row r="17" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B17" s="7"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
     </row>
     <row r="18" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B18" s="7"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
     </row>
     <row r="19" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="7"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
     </row>
     <row r="20" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B20" s="7"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
     </row>
     <row r="21" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B21" s="7"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
     </row>
     <row r="22" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B22" s="7"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="7"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="5"/>
     </row>
     <row r="23" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B23" s="7"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
     </row>
     <row r="24" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B24" s="7"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
     </row>
     <row r="25" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B25" s="7"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
     </row>
     <row r="26" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B26" s="7"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
     </row>
     <row r="27" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B27" s="7"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
     </row>
     <row r="28" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B28" s="7"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
     </row>
     <row r="29" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B29" s="7"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="7"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="5"/>
     </row>
     <row r="30" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B30" s="7"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
     </row>
     <row r="31" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B31" s="7"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
     </row>
     <row r="32" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B32" s="7"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
     </row>
     <row r="33" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B33" s="9"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
     </row>
     <row r="34" spans="2:8" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
     </row>
     <row r="36" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F36" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="G36" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H36" s="4" t="s">
+      <c r="H36" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="5"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
     </row>
     <row r="38" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B38" s="7"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
     </row>
     <row r="39" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B39" s="7"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="7"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="5"/>
     </row>
     <row r="40" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="7"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="7"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
     </row>
     <row r="41" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B41" s="7"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="7"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
     </row>
     <row r="42" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B42" s="7"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="7"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
     </row>
     <row r="43" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B43" s="7"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="7"/>
-      <c r="H43" s="7"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
     </row>
     <row r="44" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B44" s="7"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
     </row>
     <row r="45" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B45" s="7"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
-      <c r="G45" s="7"/>
-      <c r="H45" s="7"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
     </row>
     <row r="46" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B46" s="7"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8"/>
-      <c r="H46" s="7"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="5"/>
     </row>
     <row r="47" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B47" s="7"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="7"/>
-      <c r="H47" s="7"/>
+      <c r="B47" s="5"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
     </row>
     <row r="48" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="7"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="7"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
     </row>
     <row r="49" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="7"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7"/>
-      <c r="G49" s="7"/>
-      <c r="H49" s="7"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
     </row>
     <row r="50" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B50" s="7"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="7"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
     </row>
     <row r="51" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B51" s="7"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="7"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
     </row>
     <row r="52" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B52" s="7"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="7"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
     </row>
     <row r="53" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B53" s="7"/>
-      <c r="C53" s="8"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="8"/>
-      <c r="G53" s="8"/>
-      <c r="H53" s="7"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="5"/>
     </row>
     <row r="54" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B54" s="7"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
     </row>
     <row r="55" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B55" s="7"/>
-      <c r="C55" s="8"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
-      <c r="G55" s="7"/>
-      <c r="H55" s="7"/>
+      <c r="B55" s="5"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
     </row>
     <row r="56" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B56" s="7"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="7"/>
-      <c r="G56" s="7"/>
-      <c r="H56" s="7"/>
+      <c r="B56" s="5"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="5"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="5"/>
     </row>
     <row r="57" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B57" s="9"/>
-      <c r="C57" s="10"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9"/>
-      <c r="G57" s="9"/>
-      <c r="H57" s="9"/>
+      <c r="B57" s="7"/>
+      <c r="C57" s="8"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="7"/>
+      <c r="G57" s="7"/>
+      <c r="H57" s="7"/>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B58" s="11"/>
+      <c r="C58" s="11"/>
+      <c r="D58" s="11"/>
+      <c r="E58" s="11"/>
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1055,6 +1132,7 @@
     <mergeCell ref="B35:H35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="55" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="54" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>